--- a/public/downloads/LiScreening2021.xlsx
+++ b/public/downloads/LiScreening2021.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>C</t>
@@ -656,10 +679,10 @@
         <v>337</v>
       </c>
       <c r="N3" s="5">
-        <v>5293.92963051796</v>
+        <v>5293929.63051796</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03330814298983226</v>
+        <v>33.30814298983226</v>
       </c>
       <c r="P3" s="5">
         <v>158938</v>
@@ -706,10 +729,10 @@
         <v>337</v>
       </c>
       <c r="N4" s="5">
-        <v>2883.395805835724</v>
+        <v>2883395.805835724</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04076104844337245</v>
+        <v>40.76104844337245</v>
       </c>
       <c r="P4" s="5">
         <v>70739</v>
@@ -756,10 +779,10 @@
         <v>337</v>
       </c>
       <c r="N5" s="5">
-        <v>5739.934684038162</v>
+        <v>5739934.684038162</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1294439862895646</v>
+        <v>129.4439862895646</v>
       </c>
       <c r="P5" s="5">
         <v>44343</v>
@@ -806,10 +829,10 @@
         <v>337</v>
       </c>
       <c r="N6" s="5">
-        <v>5110.727120399475</v>
+        <v>5110727.120399475</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08290444019724678</v>
+        <v>82.90444019724679</v>
       </c>
       <c r="P6" s="5">
         <v>61646</v>
@@ -856,10 +879,10 @@
         <v>337</v>
       </c>
       <c r="N7" s="5">
-        <v>9089.99343252182</v>
+        <v>9089993.43252182</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1502279604766613</v>
+        <v>150.2279604766613</v>
       </c>
       <c r="P7" s="5">
         <v>60508</v>
@@ -906,10 +929,10 @@
         <v>337</v>
       </c>
       <c r="N8" s="5">
-        <v>636.4289746284485</v>
+        <v>636428.9746284485</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01204855883208603</v>
+        <v>12.04855883208604</v>
       </c>
       <c r="P8" s="5">
         <v>52822</v>
@@ -956,10 +979,10 @@
         <v>337</v>
       </c>
       <c r="N9" s="5">
-        <v>1822.301069498062</v>
+        <v>1822301.069498062</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02853632329817351</v>
+        <v>28.53632329817351</v>
       </c>
       <c r="P9" s="5">
         <v>63859</v>
@@ -1006,10 +1029,10 @@
         <v>337</v>
       </c>
       <c r="N10" s="5">
-        <v>5090.987261295319</v>
+        <v>5090987.261295319</v>
       </c>
       <c r="O10" s="4">
-        <v>0.09434568042281126</v>
+        <v>94.34568042281126</v>
       </c>
       <c r="P10" s="5">
         <v>53961</v>
@@ -1056,10 +1079,10 @@
         <v>337</v>
       </c>
       <c r="N11" s="5">
-        <v>4209.777990579605</v>
+        <v>4209777.990579605</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03995044356421926</v>
+        <v>39.95044356421926</v>
       </c>
       <c r="P11" s="5">
         <v>105375</v>
@@ -1106,10 +1129,10 @@
         <v>337</v>
       </c>
       <c r="N12" s="5">
-        <v>1005.337497472763</v>
+        <v>1005337.497472763</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01767875037319998</v>
+        <v>17.67875037319998</v>
       </c>
       <c r="P12" s="5">
         <v>56867</v>
@@ -1156,10 +1179,10 @@
         <v>337</v>
       </c>
       <c r="N13" s="5">
-        <v>9267.405798196793</v>
+        <v>9267405.798196793</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07694177354518413</v>
+        <v>76.94177354518412</v>
       </c>
       <c r="P13" s="5">
         <v>120447</v>
@@ -1206,10 +1229,10 @@
         <v>337</v>
       </c>
       <c r="N14" s="5">
-        <v>8407.461004734039</v>
+        <v>8407461.004734039</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2101182366914263</v>
+        <v>210.1182366914263</v>
       </c>
       <c r="P14" s="5">
         <v>40013</v>
@@ -1256,10 +1279,10 @@
         <v>337</v>
       </c>
       <c r="N15" s="5">
-        <v>11566.00502800941</v>
+        <v>11566005.02800941</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2139752655358521</v>
+        <v>213.9752655358521</v>
       </c>
       <c r="P15" s="5">
         <v>54053</v>
@@ -1306,10 +1329,10 @@
         <v>337</v>
       </c>
       <c r="N16" s="5">
-        <v>4174.654386281967</v>
+        <v>4174654.386281967</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09665565479572057</v>
+        <v>96.65565479572057</v>
       </c>
       <c r="P16" s="5">
         <v>43191</v>
@@ -1356,10 +1379,10 @@
         <v>337</v>
       </c>
       <c r="N17" s="5">
-        <v>5253.674499511719</v>
+        <v>5253674.499511719</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09765557268879362</v>
+        <v>97.65557268879361</v>
       </c>
       <c r="P17" s="5">
         <v>53798</v>
@@ -1387,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1398,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1434,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1457,91 +1494,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.728931934062973</v>
+        <v>1.357711602378801</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5464903547353241</v>
+        <v>1.04281292574717</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6774919985804267</v>
+        <v>1.142906532209322</v>
       </c>
       <c r="E3" s="4">
-        <v>69.93740691542902</v>
+        <v>74.99698104093703</v>
       </c>
       <c r="F3" s="4">
-        <v>78.67254411394808</v>
+        <v>81.82379571899473</v>
       </c>
       <c r="G3" s="5">
         <v>169</v>
       </c>
       <c r="H3" s="5">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>35</v>
+      </c>
+      <c r="M3" s="5">
         <v>2</v>
       </c>
-      <c r="L3" s="5">
-        <v>42</v>
-      </c>
-      <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.168493386786412</v>
+      </c>
+      <c r="O3" s="5">
+        <v>132</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5518301644836545</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2671836784516655</v>
+      </c>
+      <c r="R3" s="5">
+        <v>131</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4858006059864938</v>
+        <v>1.027675137348213</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2503312792021423</v>
+        <v>0.6875866673164615</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4183933885133854</v>
+        <v>1.418900604969505</v>
       </c>
       <c r="E4" s="4">
-        <v>70.08260447035948</v>
+        <v>70.94205539358583</v>
       </c>
       <c r="F4" s="4">
-        <v>78.89141898370107</v>
+        <v>77.36916746564441</v>
       </c>
       <c r="G4" s="5">
         <v>168</v>
       </c>
       <c r="H4" s="5">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4" s="5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.09264054340446221</v>
+      </c>
+      <c r="O4" s="5">
+        <v>122</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.039297060969123</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7566283661756458</v>
+      </c>
+      <c r="R4" s="5">
+        <v>120</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1552,6 +1643,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1559,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1570,9 +1662,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1606,8 +1704,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1629,91 +1735,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9150425321594433</v>
+        <v>1.723434407053758</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6561842005884105</v>
+        <v>1.154977620341289</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7623552198807756</v>
+        <v>1.233328775372735</v>
       </c>
       <c r="E3" s="4">
-        <v>73.15682486012174</v>
+        <v>64.89977055911125</v>
       </c>
       <c r="F3" s="4">
-        <v>79.82678739261092</v>
+        <v>72.57614868353096</v>
       </c>
       <c r="G3" s="5">
         <v>169</v>
       </c>
       <c r="H3" s="5">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="K3" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3" s="5">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>8</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.340436570470952</v>
+      </c>
+      <c r="O3" s="5">
+        <v>109</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8486029784616461</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4202366870467086</v>
+      </c>
+      <c r="R3" s="5">
+        <v>107</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.999689843592693</v>
+        <v>0.940642441194369</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1397418648876265</v>
+        <v>0.528886027116108</v>
       </c>
       <c r="D4" s="4">
-        <v>3.784173504472769</v>
+        <v>0.7795285530359958</v>
       </c>
       <c r="E4" s="4">
-        <v>67.89662293488823</v>
+        <v>64.84693877551018</v>
       </c>
       <c r="F4" s="4">
-        <v>73.53014807712773</v>
+        <v>73.49139767763852</v>
       </c>
       <c r="G4" s="5">
         <v>168</v>
       </c>
       <c r="H4" s="5">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="I4" s="5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J4" s="5">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="K4" s="5">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="L4" s="5">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="M4" s="5">
-        <v>19</v>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1655110365455759</v>
+      </c>
+      <c r="O4" s="5">
+        <v>107</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9558456883015894</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5320708644215992</v>
+      </c>
+      <c r="R4" s="5">
+        <v>107</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1724,6 +1884,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1742,9 +1903,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1778,8 +1945,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1801,91 +1976,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9061047200380771</v>
+        <v>0.728931934062973</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6937154067714326</v>
+        <v>0.5464903547353241</v>
       </c>
       <c r="D3" s="4">
-        <v>0.794631071831449</v>
+        <v>0.6774919985804267</v>
       </c>
       <c r="E3" s="4">
-        <v>74.09632492050078</v>
+        <v>69.93740691542902</v>
       </c>
       <c r="F3" s="4">
-        <v>82.04810505275185</v>
+        <v>78.67254411394808</v>
       </c>
       <c r="G3" s="5">
         <v>169</v>
       </c>
       <c r="H3" s="5">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="K3" s="5">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>42</v>
+      </c>
+      <c r="M3" s="5">
         <v>4</v>
       </c>
-      <c r="L3" s="5">
-        <v>25</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3418242685192335</v>
+      </c>
+      <c r="O3" s="5">
+        <v>125</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6260036425421844</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3920989440796457</v>
+      </c>
+      <c r="R3" s="5">
+        <v>120</v>
+      </c>
+      <c r="S3" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.319422648891392</v>
+        <v>0.4858006059864938</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4795006190783599</v>
+        <v>0.2503312792021423</v>
       </c>
       <c r="D4" s="4">
-        <v>2.499548856029531</v>
+        <v>0.4183933885133854</v>
       </c>
       <c r="E4" s="4">
-        <v>67.08738257207642</v>
+        <v>70.08260447035948</v>
       </c>
       <c r="F4" s="4">
-        <v>72.71452540747853</v>
+        <v>78.89141898370107</v>
       </c>
       <c r="G4" s="5">
         <v>168</v>
       </c>
       <c r="H4" s="5">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="I4" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K4" s="5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M4" s="5">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.03927782649114435</v>
+      </c>
+      <c r="O4" s="5">
+        <v>130</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4771576040625731</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2356275574001853</v>
+      </c>
+      <c r="R4" s="5">
+        <v>130</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1896,6 +2125,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1903,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1914,9 +2144,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1950,8 +2186,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1973,91 +2217,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.166228716092522</v>
+        <v>0.9150425321594433</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8990642055460252</v>
+        <v>0.6561842005884105</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9725386272833279</v>
+        <v>0.7623552198807756</v>
       </c>
       <c r="E3" s="4">
-        <v>76.67672986354313</v>
+        <v>73.15682486012174</v>
       </c>
       <c r="F3" s="4">
-        <v>83.39296824325321</v>
+        <v>79.82678739261092</v>
       </c>
       <c r="G3" s="5">
         <v>169</v>
       </c>
       <c r="H3" s="5">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6725300442544336</v>
+      </c>
+      <c r="O3" s="5">
+        <v>130</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5494485698725978</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2861081708967087</v>
+      </c>
+      <c r="R3" s="5">
+        <v>128</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.346785505142029</v>
+        <v>1.999689843592693</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3679672572519191</v>
+        <v>0.1397418648876265</v>
       </c>
       <c r="D4" s="4">
-        <v>3.213285137318596</v>
+        <v>3.784173504472769</v>
       </c>
       <c r="E4" s="4">
-        <v>64.67261904761891</v>
+        <v>67.89662293488823</v>
       </c>
       <c r="F4" s="4">
-        <v>67.96999840204487</v>
+        <v>73.53014807712773</v>
       </c>
       <c r="G4" s="5">
         <v>168</v>
       </c>
       <c r="H4" s="5">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I4" s="5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J4" s="5">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K4" s="5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L4" s="5">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M4" s="5">
-        <v>4</v>
+        <v>19</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.7992787389827271</v>
+      </c>
+      <c r="O4" s="5">
+        <v>97</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.01154005027286</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7934745191303068</v>
+      </c>
+      <c r="R4" s="5">
+        <v>80</v>
+      </c>
+      <c r="S4" s="5">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2068,6 +2366,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2075,7 +2374,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2086,9 +2385,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2122,8 +2427,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2145,91 +2458,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6982798034217221</v>
+        <v>0.9061047200380771</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3418072354956233</v>
+        <v>0.6937154067714326</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5276399282332862</v>
+        <v>0.794631071831449</v>
       </c>
       <c r="E3" s="4">
-        <v>81.79708569818507</v>
+        <v>74.09632492050078</v>
       </c>
       <c r="F3" s="4">
-        <v>86.16834120964174</v>
+        <v>82.04810505275185</v>
       </c>
       <c r="G3" s="5">
         <v>169</v>
       </c>
       <c r="H3" s="5">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
         <v>30</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.7471669251286074</v>
+      </c>
+      <c r="O3" s="5">
+        <v>137</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4880710592928901</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2735738329318242</v>
+      </c>
+      <c r="R3" s="5">
+        <v>136</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5363984366998508</v>
+        <v>1.319422648891392</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1263734676992956</v>
+        <v>0.4795006190783599</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3151900724993271</v>
+        <v>2.499548856029531</v>
       </c>
       <c r="E4" s="4">
-        <v>81.22529964366686</v>
+        <v>67.08738257207642</v>
       </c>
       <c r="F4" s="4">
-        <v>85.89698519228621</v>
+        <v>72.71452540747853</v>
       </c>
       <c r="G4" s="5">
         <v>168</v>
       </c>
       <c r="H4" s="5">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J4" s="5">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L4" s="5">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.3196612843139117</v>
+      </c>
+      <c r="O4" s="5">
+        <v>96</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.344305605190472</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.66980130740029</v>
+      </c>
+      <c r="R4" s="5">
+        <v>91</v>
+      </c>
+      <c r="S4" s="5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2240,6 +2607,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2247,7 +2615,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2258,9 +2626,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2294,8 +2668,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,91 +2699,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8616946770733029</v>
+        <v>1.166228716092522</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5556218447146053</v>
+        <v>0.8990642055460252</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7454678221506066</v>
+        <v>0.9725386272833279</v>
       </c>
       <c r="E3" s="4">
-        <v>74.25431711146005</v>
+        <v>76.67672986354313</v>
       </c>
       <c r="F3" s="4">
-        <v>82.55060032034818</v>
+        <v>83.39296824325321</v>
       </c>
       <c r="G3" s="5">
         <v>169</v>
       </c>
       <c r="H3" s="5">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.004359856195232</v>
+      </c>
+      <c r="O3" s="5">
+        <v>141</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.464042114241135</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2234784406090798</v>
+      </c>
+      <c r="R3" s="5">
+        <v>140</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8787553964705973</v>
+        <v>1.346785505142029</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5024469890426186</v>
+        <v>0.3679672572519191</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6835984761147229</v>
+        <v>3.213285137318596</v>
       </c>
       <c r="E4" s="4">
-        <v>74.44545675413053</v>
+        <v>64.67261904761891</v>
       </c>
       <c r="F4" s="4">
-        <v>82.91213912858208</v>
+        <v>67.96999840204487</v>
       </c>
       <c r="G4" s="5">
         <v>168</v>
       </c>
       <c r="H4" s="5">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J4" s="5">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="K4" s="5">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="L4" s="5">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2106044459234751</v>
+      </c>
+      <c r="O4" s="5">
+        <v>78</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.34847244948106</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2088692833688707</v>
+      </c>
+      <c r="R4" s="5">
+        <v>74</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2412,6 +2848,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2419,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2430,9 +2867,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2466,8 +2909,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2489,66 +2940,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7734165565664349</v>
+        <v>0.6982798034217221</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3902614827472594</v>
+        <v>0.3418072354956233</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5815163453586339</v>
+        <v>0.5276399282332862</v>
       </c>
       <c r="E3" s="4">
-        <v>81.41468421688211</v>
+        <v>81.79708569818507</v>
       </c>
       <c r="F3" s="4">
-        <v>85.69066624306731</v>
+        <v>86.16834120964174</v>
       </c>
       <c r="G3" s="5">
         <v>169</v>
       </c>
       <c r="H3" s="5">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3814382444918052</v>
+      </c>
+      <c r="O3" s="5">
+        <v>140</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6262315397711914</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3192697984652646</v>
+      </c>
+      <c r="R3" s="5">
+        <v>139</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.555277239005177</v>
+        <v>0.5363984366998508</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1278456022170684</v>
+        <v>0.1263734676992956</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3282737024566043</v>
+        <v>0.3151900724993271</v>
       </c>
       <c r="E4" s="4">
-        <v>81.19169096209876</v>
+        <v>81.22529964366686</v>
       </c>
       <c r="F4" s="4">
-        <v>85.96163577287702</v>
+        <v>85.89698519228621</v>
       </c>
       <c r="G4" s="5">
         <v>168</v>
@@ -2571,9 +3058,27 @@
       <c r="M4" s="5">
         <v>1</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.1328005834556801</v>
+      </c>
+      <c r="O4" s="5">
+        <v>138</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5801932952910039</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2023731002744371</v>
+      </c>
+      <c r="R4" s="5">
+        <v>137</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2584,6 +3089,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +3097,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2602,9 +3108,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2638,8 +3150,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2661,91 +3181,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.819302086724698</v>
+        <v>0.8616946770733029</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5141788144314005</v>
+        <v>0.5556218447146053</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6719537987279821</v>
+        <v>0.7454678221506066</v>
       </c>
       <c r="E3" s="4">
-        <v>74.29175220384018</v>
+        <v>74.25431711146005</v>
       </c>
       <c r="F3" s="4">
-        <v>82.29544762585424</v>
+        <v>82.55060032034818</v>
       </c>
       <c r="G3" s="5">
         <v>169</v>
       </c>
       <c r="H3" s="5">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6542326180722375</v>
+      </c>
+      <c r="O3" s="5">
+        <v>137</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4986262480436134</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2216881734587042</v>
+      </c>
+      <c r="R3" s="5">
+        <v>136</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.008318409975625</v>
+        <v>0.8787553964705973</v>
       </c>
       <c r="C4" s="4">
-        <v>0.663740419647352</v>
+        <v>0.5024469890426186</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7866021838087899</v>
+        <v>0.6835984761147229</v>
       </c>
       <c r="E4" s="4">
-        <v>73.58296890184654</v>
+        <v>74.44545675413053</v>
       </c>
       <c r="F4" s="4">
-        <v>81.41099392777376</v>
+        <v>82.91213912858208</v>
       </c>
       <c r="G4" s="5">
         <v>168</v>
       </c>
       <c r="H4" s="5">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4" s="5">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.4938461765112597</v>
+      </c>
+      <c r="O4" s="5">
+        <v>138</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4909791910866408</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1212914837320141</v>
+      </c>
+      <c r="R4" s="5">
+        <v>138</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2756,12 +3330,1352 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7734165565664349</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3902614827472594</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5815163453586339</v>
+      </c>
+      <c r="E3" s="4">
+        <v>81.41468421688211</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.69066624306731</v>
+      </c>
+      <c r="G3" s="5">
+        <v>169</v>
+      </c>
+      <c r="H3" s="5">
+        <v>138</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>31</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>29</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4206083388833332</v>
+      </c>
+      <c r="O3" s="5">
+        <v>139</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.653091250961084</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.310092926390366</v>
+      </c>
+      <c r="R3" s="5">
+        <v>138</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.555277239005177</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1278456022170684</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3282737024566043</v>
+      </c>
+      <c r="E4" s="4">
+        <v>81.19169096209876</v>
+      </c>
+      <c r="F4" s="4">
+        <v>85.96163577287702</v>
+      </c>
+      <c r="G4" s="5">
+        <v>168</v>
+      </c>
+      <c r="H4" s="5">
+        <v>137</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>31</v>
+      </c>
+      <c r="K4" s="5">
+        <v>4</v>
+      </c>
+      <c r="L4" s="5">
+        <v>26</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1593210655915192</v>
+      </c>
+      <c r="O4" s="5">
+        <v>138</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5875328152486399</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1888278722564349</v>
+      </c>
+      <c r="R4" s="5">
+        <v>137</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.819302086724698</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5141788144314005</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6719537987279821</v>
+      </c>
+      <c r="E3" s="4">
+        <v>74.29175220384018</v>
+      </c>
+      <c r="F3" s="4">
+        <v>82.29544762585424</v>
+      </c>
+      <c r="G3" s="5">
+        <v>169</v>
+      </c>
+      <c r="H3" s="5">
+        <v>134</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>34</v>
+      </c>
+      <c r="K3" s="5">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>31</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.5806856698453571</v>
+      </c>
+      <c r="O3" s="5">
+        <v>135</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.508788186317734</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2217912067545159</v>
+      </c>
+      <c r="R3" s="5">
+        <v>134</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.008318409975625</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.663740419647352</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.7866021838087899</v>
+      </c>
+      <c r="E4" s="4">
+        <v>73.58296890184654</v>
+      </c>
+      <c r="F4" s="4">
+        <v>81.41099392777376</v>
+      </c>
+      <c r="G4" s="5">
+        <v>168</v>
+      </c>
+      <c r="H4" s="5">
+        <v>133</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>34</v>
+      </c>
+      <c r="K4" s="5">
+        <v>3</v>
+      </c>
+      <c r="L4" s="5">
+        <v>31</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.6301274403694558</v>
+      </c>
+      <c r="O4" s="5">
+        <v>133</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5893289509105257</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2270866784460266</v>
+      </c>
+      <c r="R4" s="5">
+        <v>133</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>58.45697329376854</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5.637982195845697</v>
+      </c>
+      <c r="D3" s="3">
+        <v>35.90504451038576</v>
+      </c>
+      <c r="E3" s="3">
+        <v>11.27596439169139</v>
+      </c>
+      <c r="F3" s="3">
+        <v>23.44213649851632</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.186943620178042</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.8681354090233006</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2642578914220283</v>
+      </c>
+      <c r="J3" s="4">
+        <v>1.601062984949555</v>
+      </c>
+      <c r="K3" s="4">
+        <v>70.95369304992023</v>
+      </c>
+      <c r="L3" s="4">
+        <v>75.34194332145043</v>
+      </c>
+      <c r="M3" s="5">
+        <v>337</v>
+      </c>
+      <c r="N3" s="5">
+        <v>5293929.63051796</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.30814298983226</v>
+      </c>
+      <c r="P3" s="5">
+        <v>158938</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>67.95252225519289</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.8902077151335311</v>
+      </c>
+      <c r="D4" s="3">
+        <v>31.15727002967359</v>
+      </c>
+      <c r="E4" s="3">
+        <v>8.30860534124629</v>
+      </c>
+      <c r="F4" s="3">
+        <v>22.55192878338279</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.2967359050445104</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.6755342083066684</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2981794874374755</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.4564550704245878</v>
+      </c>
+      <c r="K4" s="4">
+        <v>64.63099779971333</v>
+      </c>
+      <c r="L4" s="4">
+        <v>73.74780103426075</v>
+      </c>
+      <c r="M4" s="5">
+        <v>337</v>
+      </c>
+      <c r="N4" s="5">
+        <v>2883395.805835724</v>
+      </c>
+      <c r="O4" s="4">
+        <v>40.76104844337245</v>
+      </c>
+      <c r="P4" s="5">
+        <v>70739</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>81.89910979228486</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.8902077151335311</v>
+      </c>
+      <c r="D5" s="3">
+        <v>17.2106824925816</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.780415430267062</v>
+      </c>
+      <c r="F5" s="3">
+        <v>15.13353115727003</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.2967359050445104</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.4677151990667567</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2343348052169627</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.5026225111046877</v>
+      </c>
+      <c r="K5" s="4">
+        <v>76.15131512545685</v>
+      </c>
+      <c r="L5" s="4">
+        <v>83.42540776292955</v>
+      </c>
+      <c r="M5" s="5">
+        <v>337</v>
+      </c>
+      <c r="N5" s="5">
+        <v>5739934.684038162</v>
+      </c>
+      <c r="O5" s="4">
+        <v>129.4439862895646</v>
+      </c>
+      <c r="P5" s="5">
+        <v>44343</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>66.46884272997032</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3.264094955489615</v>
+      </c>
+      <c r="D6" s="3">
+        <v>30.26706231454006</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.967359050445104</v>
+      </c>
+      <c r="F6" s="3">
+        <v>26.11275964391692</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1.186943620178042</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.8457028967925567</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3583732902773425</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.6035285988989524</v>
+      </c>
+      <c r="K6" s="4">
+        <v>68.13631684127657</v>
+      </c>
+      <c r="L6" s="4">
+        <v>75.26052350321002</v>
+      </c>
+      <c r="M6" s="5">
+        <v>337</v>
+      </c>
+      <c r="N6" s="5">
+        <v>5110727.120399475</v>
+      </c>
+      <c r="O6" s="4">
+        <v>82.90444019724679</v>
+      </c>
+      <c r="P6" s="5">
+        <v>61646</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>75.07418397626114</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.5934718100890208</v>
+      </c>
+      <c r="D7" s="3">
+        <v>24.33234421364985</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3.560830860534125</v>
+      </c>
+      <c r="F7" s="3">
+        <v>17.80415430267063</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.967359050445104</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.8124887376408301</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.3707814937595443</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.8440717926726103</v>
+      </c>
+      <c r="K7" s="4">
+        <v>75.78423060618911</v>
+      </c>
+      <c r="L7" s="4">
+        <v>81.8523091629653</v>
+      </c>
+      <c r="M7" s="5">
+        <v>337</v>
+      </c>
+      <c r="N7" s="5">
+        <v>9089993.43252182</v>
+      </c>
+      <c r="O7" s="4">
+        <v>150.2279604766613</v>
+      </c>
+      <c r="P7" s="5">
+        <v>60508</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>74.4807121661721</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3.560830860534125</v>
+      </c>
+      <c r="D8" s="3">
+        <v>21.95845697329377</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>21.06824925816024</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.8902077151335311</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.7948403680728493</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.5011811387181102</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.8958357123538176</v>
+      </c>
+      <c r="K8" s="4">
+        <v>72.97553442742085</v>
+      </c>
+      <c r="L8" s="4">
+        <v>79.60309083305161</v>
+      </c>
+      <c r="M8" s="5">
+        <v>337</v>
+      </c>
+      <c r="N8" s="5">
+        <v>636428.9746284485</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.04855883208604</v>
+      </c>
+      <c r="P8" s="5">
+        <v>52822</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>63.50148367952523</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4.451038575667656</v>
+      </c>
+      <c r="D9" s="3">
+        <v>32.04747774480713</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.560830860534125</v>
+      </c>
+      <c r="F9" s="3">
+        <v>27.89317507418398</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.5934718100890208</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.9020652195687989</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.4761537757341539</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.6679228293416828</v>
+      </c>
+      <c r="K9" s="4">
+        <v>64.87343305274628</v>
+      </c>
+      <c r="L9" s="4">
+        <v>73.03241524439265</v>
+      </c>
+      <c r="M9" s="5">
+        <v>337</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1822301.069498062</v>
+      </c>
+      <c r="O9" s="4">
+        <v>28.53632329817351</v>
+      </c>
+      <c r="P9" s="5">
+        <v>63859</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>74.1839762611276</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>25.8160237388724</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.780415430267062</v>
+      </c>
+      <c r="F10" s="3">
+        <v>22.55192878338279</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1.483679525222552</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.5518014631220814</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3107338230063263</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.5268752735924671</v>
+      </c>
+      <c r="K10" s="4">
+        <v>70.00979026625485</v>
+      </c>
+      <c r="L10" s="4">
+        <v>78.78165680866165</v>
+      </c>
+      <c r="M10" s="5">
+        <v>337</v>
+      </c>
+      <c r="N10" s="5">
+        <v>5090987.261295319</v>
+      </c>
+      <c r="O10" s="4">
+        <v>94.34568042281126</v>
+      </c>
+      <c r="P10" s="5">
+        <v>53961</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>61.72106824925816</v>
+      </c>
+      <c r="C11" s="3">
+        <v>7.121661721068249</v>
+      </c>
+      <c r="D11" s="3">
+        <v>31.15727002967359</v>
+      </c>
+      <c r="E11" s="3">
+        <v>10.08902077151335</v>
+      </c>
+      <c r="F11" s="3">
+        <v>15.43026706231454</v>
+      </c>
+      <c r="G11" s="3">
+        <v>5.637982195845697</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1.278325034879257</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.4812490740634772</v>
+      </c>
+      <c r="J11" s="4">
+        <v>2.082717868382159</v>
+      </c>
+      <c r="K11" s="4">
+        <v>70.53452835139981</v>
+      </c>
+      <c r="L11" s="4">
+        <v>76.68780992970029</v>
+      </c>
+      <c r="M11" s="5">
+        <v>337</v>
+      </c>
+      <c r="N11" s="5">
+        <v>4209777.990579605</v>
+      </c>
+      <c r="O11" s="4">
+        <v>39.95044356421926</v>
+      </c>
+      <c r="P11" s="5">
+        <v>105375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>67.35905044510386</v>
+      </c>
+      <c r="C12" s="3">
+        <v>4.747774480712167</v>
+      </c>
+      <c r="D12" s="3">
+        <v>27.89317507418398</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5.934718100890208</v>
+      </c>
+      <c r="F12" s="3">
+        <v>20.1780415430267</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1.780415430267062</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.9149179545771449</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.4324139218156585</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1.448848222206412</v>
+      </c>
+      <c r="K12" s="4">
+        <v>70.60225277054452</v>
+      </c>
+      <c r="L12" s="4">
+        <v>77.39516327113164</v>
+      </c>
+      <c r="M12" s="5">
+        <v>337</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1005337.497472763</v>
+      </c>
+      <c r="O12" s="4">
+        <v>17.67875037319998</v>
+      </c>
+      <c r="P12" s="5">
+        <v>56867</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>63.50148367952523</v>
+      </c>
+      <c r="C13" s="3">
+        <v>5.341246290801187</v>
+      </c>
+      <c r="D13" s="3">
+        <v>31.15727002967359</v>
+      </c>
+      <c r="E13" s="3">
+        <v>9.495548961424333</v>
+      </c>
+      <c r="F13" s="3">
+        <v>20.1780415430267</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1.483679525222552</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.9049450706812165</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2184266759559234</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1.796860156854991</v>
+      </c>
+      <c r="K13" s="4">
+        <v>70.69248470901719</v>
+      </c>
+      <c r="L13" s="4">
+        <v>75.70436606722072</v>
+      </c>
+      <c r="M13" s="5">
+        <v>337</v>
+      </c>
+      <c r="N13" s="5">
+        <v>9267405.798196793</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.94177354518412</v>
+      </c>
+      <c r="P13" s="5">
+        <v>120447</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>81.89910979228486</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>18.10089020771514</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2.077151335311572</v>
+      </c>
+      <c r="F14" s="3">
+        <v>15.43026706231454</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.5934718100890208</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.6032807235318101</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.2612449881314118</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.4249694841102535</v>
+      </c>
+      <c r="K14" s="4">
+        <v>81.51204101818755</v>
+      </c>
+      <c r="L14" s="4">
+        <v>86.03306580633293</v>
+      </c>
+      <c r="M14" s="5">
+        <v>337</v>
+      </c>
+      <c r="N14" s="5">
+        <v>8407461.004734039</v>
+      </c>
+      <c r="O14" s="4">
+        <v>210.1182366914263</v>
+      </c>
+      <c r="P14" s="5">
+        <v>40013</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>81.30563798219585</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>18.69436201780415</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2.670623145400593</v>
+      </c>
+      <c r="F15" s="3">
+        <v>15.72700296735905</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.2967359050445104</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.4948140653469624</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1711234173189844</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.3688215761392443</v>
+      </c>
+      <c r="K15" s="4">
+        <v>74.34960334282091</v>
+      </c>
+      <c r="L15" s="4">
+        <v>82.73083331673857</v>
+      </c>
+      <c r="M15" s="5">
+        <v>337</v>
+      </c>
+      <c r="N15" s="5">
+        <v>11566005.02800941</v>
+      </c>
+      <c r="O15" s="4">
+        <v>213.9752655358521</v>
+      </c>
+      <c r="P15" s="5">
+        <v>54053</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>81.60237388724035</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>18.39762611275964</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.483679525222552</v>
+      </c>
+      <c r="F16" s="3">
+        <v>16.32047477744807</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.5934718100890208</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.6204093008136342</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2496808812400075</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.4314788293075575</v>
+      </c>
+      <c r="K16" s="4">
+        <v>81.30351844001704</v>
+      </c>
+      <c r="L16" s="4">
+        <v>85.82574897602838</v>
+      </c>
+      <c r="M16" s="5">
+        <v>337</v>
+      </c>
+      <c r="N16" s="5">
+        <v>4174654.386281967</v>
+      </c>
+      <c r="O16" s="4">
+        <v>96.65565479572057</v>
+      </c>
+      <c r="P16" s="5">
+        <v>43191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>79.22848664688428</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.5934718100890208</v>
+      </c>
+      <c r="D17" s="3">
+        <v>20.1780415430267</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.483679525222552</v>
+      </c>
+      <c r="F17" s="3">
+        <v>18.39762611275964</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.2967359050445104</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.5489390719307577</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2244290259866167</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.4218910003828248</v>
+      </c>
+      <c r="K17" s="4">
+        <v>73.93841216011619</v>
+      </c>
+      <c r="L17" s="4">
+        <v>81.85453302265663</v>
+      </c>
+      <c r="M17" s="5">
+        <v>337</v>
+      </c>
+      <c r="N17" s="5">
+        <v>5253674.499511719</v>
+      </c>
+      <c r="O17" s="4">
+        <v>97.65557268879361</v>
+      </c>
+      <c r="P17" s="5">
+        <v>53798</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2875,16 +4789,16 @@
         <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="L3" s="5">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -2919,16 +4833,16 @@
         <v>5</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -2963,16 +4877,16 @@
         <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3007,16 +4921,16 @@
         <v>6</v>
       </c>
       <c r="K6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
       <c r="N6" s="5">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -3051,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
       <c r="N7" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -3139,16 +5053,16 @@
         <v>4</v>
       </c>
       <c r="K9" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3186,13 +5100,13 @@
         <v>2</v>
       </c>
       <c r="L10" s="5">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="M10" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3227,16 +5141,16 @@
         <v>2</v>
       </c>
       <c r="K11" s="5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L11" s="5">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3271,16 +5185,16 @@
         <v>4</v>
       </c>
       <c r="K12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="M12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3315,16 +5229,16 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L13" s="5">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
       </c>
       <c r="N13" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3359,16 +5273,16 @@
         <v>2</v>
       </c>
       <c r="K14" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3406,13 +5320,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="M15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="5">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -3447,16 +5361,16 @@
         <v>1</v>
       </c>
       <c r="K16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3494,13 +5408,13 @@
         <v>1</v>
       </c>
       <c r="L17" s="5">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3516,9 +5430,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>197</v>
+      </c>
+      <c r="C3" s="5">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5">
+        <v>121</v>
+      </c>
+      <c r="E3" s="5">
+        <v>38</v>
+      </c>
+      <c r="F3" s="5">
+        <v>79</v>
+      </c>
+      <c r="G3" s="5">
+        <v>4</v>
+      </c>
+      <c r="H3" s="5">
+        <v>38</v>
+      </c>
+      <c r="I3" s="5">
+        <v>37</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>18</v>
+      </c>
+      <c r="L3" s="5">
+        <v>63</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>229</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>105</v>
+      </c>
+      <c r="E4" s="5">
+        <v>28</v>
+      </c>
+      <c r="F4" s="5">
+        <v>76</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>28</v>
+      </c>
+      <c r="I4" s="5">
+        <v>24</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>64</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>276</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>58</v>
+      </c>
+      <c r="E5" s="5">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5">
+        <v>51</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5">
+        <v>5</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>51</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>224</v>
+      </c>
+      <c r="C6" s="5">
+        <v>11</v>
+      </c>
+      <c r="D6" s="5">
+        <v>102</v>
+      </c>
+      <c r="E6" s="5">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5">
+        <v>88</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4</v>
+      </c>
+      <c r="H6" s="5">
+        <v>10</v>
+      </c>
+      <c r="I6" s="5">
+        <v>4</v>
+      </c>
+      <c r="J6" s="5">
+        <v>6</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>86</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>253</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>82</v>
+      </c>
+      <c r="E7" s="5">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5">
+        <v>60</v>
+      </c>
+      <c r="G7" s="5">
+        <v>10</v>
+      </c>
+      <c r="H7" s="5">
+        <v>12</v>
+      </c>
+      <c r="I7" s="5">
+        <v>12</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>57</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>251</v>
+      </c>
+      <c r="C8" s="5">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5">
+        <v>74</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>71</v>
+      </c>
+      <c r="G8" s="5">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>67</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>214</v>
+      </c>
+      <c r="C9" s="5">
+        <v>15</v>
+      </c>
+      <c r="D9" s="5">
+        <v>108</v>
+      </c>
+      <c r="E9" s="5">
+        <v>12</v>
+      </c>
+      <c r="F9" s="5">
+        <v>94</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5">
+        <v>12</v>
+      </c>
+      <c r="I9" s="5">
+        <v>9</v>
+      </c>
+      <c r="J9" s="5">
+        <v>4</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>92</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>250</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>87</v>
+      </c>
+      <c r="E10" s="5">
+        <v>6</v>
+      </c>
+      <c r="F10" s="5">
+        <v>76</v>
+      </c>
+      <c r="G10" s="5">
+        <v>5</v>
+      </c>
+      <c r="H10" s="5">
+        <v>6</v>
+      </c>
+      <c r="I10" s="5">
+        <v>2</v>
+      </c>
+      <c r="J10" s="5">
+        <v>4</v>
+      </c>
+      <c r="K10" s="5">
+        <v>2</v>
+      </c>
+      <c r="L10" s="5">
+        <v>70</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>208</v>
+      </c>
+      <c r="C11" s="5">
+        <v>24</v>
+      </c>
+      <c r="D11" s="5">
+        <v>105</v>
+      </c>
+      <c r="E11" s="5">
+        <v>34</v>
+      </c>
+      <c r="F11" s="5">
+        <v>52</v>
+      </c>
+      <c r="G11" s="5">
+        <v>19</v>
+      </c>
+      <c r="H11" s="5">
+        <v>34</v>
+      </c>
+      <c r="I11" s="5">
+        <v>33</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2</v>
+      </c>
+      <c r="K11" s="5">
+        <v>2</v>
+      </c>
+      <c r="L11" s="5">
+        <v>46</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>227</v>
+      </c>
+      <c r="C12" s="5">
+        <v>16</v>
+      </c>
+      <c r="D12" s="5">
+        <v>94</v>
+      </c>
+      <c r="E12" s="5">
+        <v>20</v>
+      </c>
+      <c r="F12" s="5">
+        <v>68</v>
+      </c>
+      <c r="G12" s="5">
+        <v>6</v>
+      </c>
+      <c r="H12" s="5">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5">
+        <v>17</v>
+      </c>
+      <c r="J12" s="5">
+        <v>4</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>66</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>214</v>
+      </c>
+      <c r="C13" s="5">
+        <v>18</v>
+      </c>
+      <c r="D13" s="5">
+        <v>105</v>
+      </c>
+      <c r="E13" s="5">
+        <v>32</v>
+      </c>
+      <c r="F13" s="5">
+        <v>68</v>
+      </c>
+      <c r="G13" s="5">
+        <v>5</v>
+      </c>
+      <c r="H13" s="5">
+        <v>32</v>
+      </c>
+      <c r="I13" s="5">
+        <v>32</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>3</v>
+      </c>
+      <c r="L13" s="5">
+        <v>64</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>276</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>61</v>
+      </c>
+      <c r="E14" s="5">
+        <v>7</v>
+      </c>
+      <c r="F14" s="5">
+        <v>52</v>
+      </c>
+      <c r="G14" s="5">
+        <v>2</v>
+      </c>
+      <c r="H14" s="5">
+        <v>7</v>
+      </c>
+      <c r="I14" s="5">
+        <v>6</v>
+      </c>
+      <c r="J14" s="5">
+        <v>2</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>51</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>274</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>63</v>
+      </c>
+      <c r="E15" s="5">
+        <v>9</v>
+      </c>
+      <c r="F15" s="5">
+        <v>53</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5">
+        <v>9</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>8</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>51</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>275</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>62</v>
+      </c>
+      <c r="E16" s="5">
+        <v>5</v>
+      </c>
+      <c r="F16" s="5">
+        <v>55</v>
+      </c>
+      <c r="G16" s="5">
+        <v>2</v>
+      </c>
+      <c r="H16" s="5">
+        <v>5</v>
+      </c>
+      <c r="I16" s="5">
+        <v>4</v>
+      </c>
+      <c r="J16" s="5">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>52</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>267</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5">
+        <v>68</v>
+      </c>
+      <c r="E17" s="5">
+        <v>5</v>
+      </c>
+      <c r="F17" s="5">
+        <v>62</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>5</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5">
+        <v>4</v>
+      </c>
+      <c r="K17" s="5">
+        <v>1</v>
+      </c>
+      <c r="L17" s="5">
+        <v>62</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3529,9 +6198,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3565,8 +6240,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3588,10 +6271,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.710584078730066</v>
@@ -3629,10 +6330,28 @@
       <c r="M3" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.567289293431915</v>
+      </c>
+      <c r="O3" s="5">
+        <v>124</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5781916307281724</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2857647861783666</v>
+      </c>
+      <c r="R3" s="5">
+        <v>123</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>1.288936320648885</v>
@@ -3670,9 +6389,27 @@
       <c r="M4" s="5">
         <v>3</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.5834387757914148</v>
+      </c>
+      <c r="O4" s="5">
+        <v>77</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.159805043141614</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2285099447324392</v>
+      </c>
+      <c r="R4" s="5">
+        <v>74</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3683,14 +6420,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3701,9 +6439,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3737,8 +6481,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,10 +6512,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.511475317229358</v>
@@ -3801,10 +6571,28 @@
       <c r="M3" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.326025901195134</v>
+      </c>
+      <c r="O3" s="5">
+        <v>118</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6562770057764341</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3723823827864512</v>
+      </c>
+      <c r="R3" s="5">
+        <v>117</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.9226720772105975</v>
@@ -3842,9 +6630,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.4113955749120533</v>
+      </c>
+      <c r="O4" s="5">
+        <v>112</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.69490603704244</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2206639628318489</v>
+      </c>
+      <c r="R4" s="5">
+        <v>112</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3855,14 +6661,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3873,9 +6680,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3909,8 +6722,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3932,10 +6753,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.8615986196382787</v>
@@ -3973,10 +6812,28 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.7081761642271932</v>
+      </c>
+      <c r="O3" s="5">
+        <v>138</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4415189905141524</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2530272284257897</v>
+      </c>
+      <c r="R3" s="5">
+        <v>137</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.6058409992177393</v>
@@ -4014,9 +6871,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.2242260190358011</v>
+      </c>
+      <c r="O4" s="5">
+        <v>139</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.494067337432174</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2159113377377592</v>
+      </c>
+      <c r="R4" s="5">
+        <v>139</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4027,14 +6902,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4045,9 +6921,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4081,8 +6963,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4104,10 +6994,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.285607965516257</v>
@@ -4145,10 +7053,28 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.8477633907596893</v>
+      </c>
+      <c r="O3" s="5">
+        <v>109</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7060100471931252</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3275538397712039</v>
+      </c>
+      <c r="R3" s="5">
+        <v>109</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.9972548210616459</v>
@@ -4186,9 +7112,27 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.05222000667834459</v>
+      </c>
+      <c r="O4" s="5">
+        <v>119</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9862272514491282</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3875847694527261</v>
+      </c>
+      <c r="R4" s="5">
+        <v>115</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4199,14 +7143,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4217,9 +7162,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4253,8 +7204,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4276,10 +7235,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.008230674681089</v>
@@ -4317,10 +7294,28 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.7876173135995779</v>
+      </c>
+      <c r="O3" s="5">
+        <v>140</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5030539161828125</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2069919646433876</v>
+      </c>
+      <c r="R3" s="5">
+        <v>139</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.9855159364356271</v>
@@ -4358,9 +7353,27 @@
       <c r="M4" s="5">
         <v>12</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.5275223736994583</v>
+      </c>
+      <c r="O4" s="5">
+        <v>123</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.123765433036098</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5704897792608232</v>
+      </c>
+      <c r="R4" s="5">
+        <v>114</v>
+      </c>
+      <c r="S4" s="5">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4371,350 +7384,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.357711602378801</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.04281292574717</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.142906532209322</v>
-      </c>
-      <c r="E3" s="4">
-        <v>74.99698104093703</v>
-      </c>
-      <c r="F3" s="4">
-        <v>81.82379571899473</v>
-      </c>
-      <c r="G3" s="5">
-        <v>169</v>
-      </c>
-      <c r="H3" s="5">
-        <v>130</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>37</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>35</v>
-      </c>
-      <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.027675137348213</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6875866673164615</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.418900604969505</v>
-      </c>
-      <c r="E4" s="4">
-        <v>70.94205539358583</v>
-      </c>
-      <c r="F4" s="4">
-        <v>77.36916746564441</v>
-      </c>
-      <c r="G4" s="5">
-        <v>168</v>
-      </c>
-      <c r="H4" s="5">
-        <v>116</v>
-      </c>
-      <c r="I4" s="5">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5">
-        <v>42</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>36</v>
-      </c>
-      <c r="M4" s="5">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.723434407053758</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.154977620341289</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.233328775372735</v>
-      </c>
-      <c r="E3" s="4">
-        <v>64.89977055911125</v>
-      </c>
-      <c r="F3" s="4">
-        <v>72.57614868353096</v>
-      </c>
-      <c r="G3" s="5">
-        <v>169</v>
-      </c>
-      <c r="H3" s="5">
-        <v>101</v>
-      </c>
-      <c r="I3" s="5">
-        <v>7</v>
-      </c>
-      <c r="J3" s="5">
-        <v>61</v>
-      </c>
-      <c r="K3" s="5">
-        <v>6</v>
-      </c>
-      <c r="L3" s="5">
-        <v>47</v>
-      </c>
-      <c r="M3" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.940642441194369</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.528886027116108</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.7795285530359958</v>
-      </c>
-      <c r="E4" s="4">
-        <v>64.84693877551018</v>
-      </c>
-      <c r="F4" s="4">
-        <v>73.49139767763852</v>
-      </c>
-      <c r="G4" s="5">
-        <v>168</v>
-      </c>
-      <c r="H4" s="5">
-        <v>107</v>
-      </c>
-      <c r="I4" s="5">
-        <v>8</v>
-      </c>
-      <c r="J4" s="5">
-        <v>53</v>
-      </c>
-      <c r="K4" s="5">
-        <v>6</v>
-      </c>
-      <c r="L4" s="5">
-        <v>47</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/LiScreening2021.xlsx
+++ b/public/downloads/LiScreening2021.xlsx
@@ -1554,16 +1554,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.168493386786412</v>
+        <v>-1.057141271506552</v>
       </c>
       <c r="O3" s="5">
         <v>132</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5518301644836545</v>
+        <v>0.5471652587117902</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2671836784516655</v>
+        <v>0.2458653032571422</v>
       </c>
       <c r="R3" s="5">
         <v>131</v>
@@ -1613,22 +1613,22 @@
         <v>6</v>
       </c>
       <c r="N4" s="4">
-        <v>0.09264054340446221</v>
+        <v>-0.4788149315916215</v>
       </c>
       <c r="O4" s="5">
         <v>122</v>
       </c>
       <c r="P4" s="4">
-        <v>1.039297060969123</v>
+        <v>1.020490303832682</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7566283661756458</v>
+        <v>0.5145849124497582</v>
       </c>
       <c r="R4" s="5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="S4" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1795,16 +1795,16 @@
         <v>8</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.340436570470952</v>
+        <v>-1.276693600892031</v>
       </c>
       <c r="O3" s="5">
         <v>109</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8486029784616461</v>
+        <v>0.8572583497083268</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4202366870467086</v>
+        <v>0.4164223171334805</v>
       </c>
       <c r="R3" s="5">
         <v>107</v>
@@ -1854,16 +1854,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1655110365455759</v>
+        <v>0.07699278338986915</v>
       </c>
       <c r="O4" s="5">
         <v>107</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9558456883015894</v>
+        <v>0.9403718407672963</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5320708644215992</v>
+        <v>0.5207541764663491</v>
       </c>
       <c r="R4" s="5">
         <v>107</v>
@@ -2036,16 +2036,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3418242685192335</v>
+        <v>-0.4428659099755521</v>
       </c>
       <c r="O3" s="5">
         <v>125</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6260036425421844</v>
+        <v>0.6253019562897562</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3920989440796457</v>
+        <v>0.3761588530750763</v>
       </c>
       <c r="R3" s="5">
         <v>120</v>
@@ -2095,16 +2095,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03927782649114435</v>
+        <v>-0.1121346953384048</v>
       </c>
       <c r="O4" s="5">
         <v>130</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4771576040625731</v>
+        <v>0.4710657345454673</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2356275574001853</v>
+        <v>0.2210105145041644</v>
       </c>
       <c r="R4" s="5">
         <v>130</v>
@@ -2277,16 +2277,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6725300442544336</v>
+        <v>-0.6138985943416628</v>
       </c>
       <c r="O3" s="5">
         <v>130</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5494485698725978</v>
+        <v>0.5507670629632316</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2861081708967087</v>
+        <v>0.2818942371736703</v>
       </c>
       <c r="R3" s="5">
         <v>128</v>
@@ -2336,22 +2336,22 @@
         <v>19</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7992787389827271</v>
+        <v>0.0731181677110726</v>
       </c>
       <c r="O4" s="5">
         <v>97</v>
       </c>
       <c r="P4" s="4">
-        <v>2.01154005027286</v>
+        <v>1.972167026994589</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7934745191303068</v>
+        <v>0.1444254958325024</v>
       </c>
       <c r="R4" s="5">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S4" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2518,16 +2518,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7471669251286074</v>
+        <v>-0.7062971501072752</v>
       </c>
       <c r="O3" s="5">
         <v>137</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4880710592928901</v>
+        <v>0.488118556792684</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2735738329318242</v>
+        <v>0.2709282380955976</v>
       </c>
       <c r="R3" s="5">
         <v>136</v>
@@ -2577,22 +2577,22 @@
         <v>6</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3196612843139117</v>
+        <v>-0.234628162568697</v>
       </c>
       <c r="O4" s="5">
         <v>96</v>
       </c>
       <c r="P4" s="4">
-        <v>1.344305605190472</v>
+        <v>1.335564801134512</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.66980130740029</v>
+        <v>0.3422453338078741</v>
       </c>
       <c r="R4" s="5">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="S4" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2759,16 +2759,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.004359856195232</v>
+        <v>-0.9238063815027999</v>
       </c>
       <c r="O3" s="5">
         <v>141</v>
       </c>
       <c r="P3" s="4">
-        <v>0.464042114241135</v>
+        <v>0.462678303464457</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2234784406090798</v>
+        <v>0.2116792287868813</v>
       </c>
       <c r="R3" s="5">
         <v>140</v>
@@ -2818,16 +2818,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2106044459234751</v>
+        <v>-0.3763354489474295</v>
       </c>
       <c r="O4" s="5">
         <v>78</v>
       </c>
       <c r="P4" s="4">
-        <v>1.34847244948106</v>
+        <v>1.383247924774963</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2088692833688707</v>
+        <v>0.1489739203729451</v>
       </c>
       <c r="R4" s="5">
         <v>74</v>
@@ -3000,16 +3000,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3814382444918052</v>
+        <v>-0.208292337927559</v>
       </c>
       <c r="O3" s="5">
         <v>140</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6262315397711914</v>
+        <v>0.6093910471893652</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3192697984652646</v>
+        <v>0.2696980002941348</v>
       </c>
       <c r="R3" s="5">
         <v>139</v>
@@ -3059,16 +3059,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1328005834556801</v>
+        <v>0.02678274982461559</v>
       </c>
       <c r="O4" s="5">
         <v>138</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5801932952910039</v>
+        <v>0.5371700233874299</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2023731002744371</v>
+        <v>0.122823272936866</v>
       </c>
       <c r="R4" s="5">
         <v>137</v>
@@ -3241,16 +3241,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6542326180722375</v>
+        <v>-0.5401797057420374</v>
       </c>
       <c r="O3" s="5">
         <v>137</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4986262480436134</v>
+        <v>0.492989262122187</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2216881734587042</v>
+        <v>0.1967488852794021</v>
       </c>
       <c r="R3" s="5">
         <v>136</v>
@@ -3300,13 +3300,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4938461765112597</v>
+        <v>-0.4952221361309199</v>
       </c>
       <c r="O4" s="5">
         <v>138</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4909791910866408</v>
+        <v>0.4907990058983521</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1212914837320141</v>
@@ -3482,16 +3482,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4206083388833332</v>
+        <v>-0.2684872182653777</v>
       </c>
       <c r="O3" s="5">
         <v>139</v>
       </c>
       <c r="P3" s="4">
-        <v>0.653091250961084</v>
+        <v>0.6343907846190731</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.310092926390366</v>
+        <v>0.2681923448038908</v>
       </c>
       <c r="R3" s="5">
         <v>138</v>
@@ -3541,16 +3541,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1593210655915192</v>
+        <v>-0.01169658310936939</v>
       </c>
       <c r="O4" s="5">
         <v>138</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5875328152486399</v>
+        <v>0.553569507521992</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1888278722564349</v>
+        <v>0.1273736036032213</v>
       </c>
       <c r="R4" s="5">
         <v>137</v>
@@ -3723,16 +3723,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5806856698453571</v>
+        <v>-0.4787145650407041</v>
       </c>
       <c r="O3" s="5">
         <v>135</v>
       </c>
       <c r="P3" s="4">
-        <v>0.508788186317734</v>
+        <v>0.5051474371927216</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2217912067545159</v>
+        <v>0.2020093687736904</v>
       </c>
       <c r="R3" s="5">
         <v>134</v>
@@ -3782,16 +3782,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6301274403694558</v>
+        <v>-0.6829610143468017</v>
       </c>
       <c r="O4" s="5">
         <v>133</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5893289509105257</v>
+        <v>0.5782000137378592</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2270866784460266</v>
+        <v>0.2205767270216777</v>
       </c>
       <c r="R4" s="5">
         <v>133</v>
@@ -3928,13 +3928,13 @@
         <v>1.186943620178042</v>
       </c>
       <c r="H3" s="4">
-        <v>0.8681354090233006</v>
+        <v>0.8787114914482491</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2642578914220283</v>
+        <v>0.2170239502136294</v>
       </c>
       <c r="J3" s="4">
-        <v>1.601062984949555</v>
+        <v>1.60119010855038</v>
       </c>
       <c r="K3" s="4">
         <v>70.95369304992023</v>
@@ -3978,13 +3978,13 @@
         <v>0.2967359050445104</v>
       </c>
       <c r="H4" s="4">
-        <v>0.6755342083066684</v>
+        <v>0.6761594722030142</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2981794874374755</v>
+        <v>0.2923558505581588</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4564550704245878</v>
+        <v>0.4451437531634785</v>
       </c>
       <c r="K4" s="4">
         <v>64.63099779971333</v>
@@ -4028,13 +4028,13 @@
         <v>0.2967359050445104</v>
       </c>
       <c r="H5" s="4">
-        <v>0.4677151990667567</v>
+        <v>0.4616331159813725</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2343348052169627</v>
+        <v>0.2249060090197215</v>
       </c>
       <c r="J5" s="4">
-        <v>0.5026225111046877</v>
+        <v>0.4955646712537971</v>
       </c>
       <c r="K5" s="4">
         <v>76.15131512545685</v>
@@ -4078,13 +4078,13 @@
         <v>1.186943620178042</v>
       </c>
       <c r="H6" s="4">
-        <v>0.8457028967925567</v>
+        <v>0.8404552720154528</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3583732902773425</v>
+        <v>0.3550050547250519</v>
       </c>
       <c r="J6" s="4">
-        <v>0.6035285988989524</v>
+        <v>0.6062889822449159</v>
       </c>
       <c r="K6" s="4">
         <v>68.13631684127657</v>
@@ -4110,13 +4110,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>75.07418397626114</v>
+        <v>74.1839762611276</v>
       </c>
       <c r="C7" s="3">
         <v>0.5934718100890208</v>
       </c>
       <c r="D7" s="3">
-        <v>24.33234421364985</v>
+        <v>25.22255192878338</v>
       </c>
       <c r="E7" s="3">
         <v>3.560830860534125</v>
@@ -4125,16 +4125,16 @@
         <v>17.80415430267063</v>
       </c>
       <c r="G7" s="3">
-        <v>2.967359050445104</v>
+        <v>3.857566765578635</v>
       </c>
       <c r="H7" s="4">
-        <v>0.8124887376408301</v>
+        <v>0.7408210353992224</v>
       </c>
       <c r="I7" s="4">
-        <v>0.3707814937595443</v>
+        <v>0.227633566938016</v>
       </c>
       <c r="J7" s="4">
-        <v>0.8440717926726103</v>
+        <v>0.7986162360429004</v>
       </c>
       <c r="K7" s="4">
         <v>75.78423060618911</v>
@@ -4160,13 +4160,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>74.4807121661721</v>
+        <v>71.51335311572701</v>
       </c>
       <c r="C8" s="3">
         <v>3.560830860534125</v>
       </c>
       <c r="D8" s="3">
-        <v>21.95845697329377</v>
+        <v>24.92581602373887</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -4175,16 +4175,16 @@
         <v>21.06824925816024</v>
       </c>
       <c r="G8" s="3">
-        <v>0.8902077151335311</v>
+        <v>3.857566765578635</v>
       </c>
       <c r="H8" s="4">
-        <v>0.7948403680728493</v>
+        <v>0.783125518594015</v>
       </c>
       <c r="I8" s="4">
-        <v>0.5011811387181102</v>
+        <v>0.3685174070380043</v>
       </c>
       <c r="J8" s="4">
-        <v>0.8958357123538176</v>
+        <v>0.903666672760853</v>
       </c>
       <c r="K8" s="4">
         <v>72.97553442742085</v>
@@ -4228,13 +4228,13 @@
         <v>0.5934718100890208</v>
       </c>
       <c r="H9" s="4">
-        <v>0.9020652195687989</v>
+        <v>0.8986917814528576</v>
       </c>
       <c r="I9" s="4">
-        <v>0.4761537757341539</v>
+        <v>0.4685882467999148</v>
       </c>
       <c r="J9" s="4">
-        <v>0.6679228293416828</v>
+        <v>0.6684748086911751</v>
       </c>
       <c r="K9" s="4">
         <v>64.87343305274628</v>
@@ -4278,13 +4278,13 @@
         <v>1.483679525222552</v>
       </c>
       <c r="H10" s="4">
-        <v>0.5518014631220814</v>
+        <v>0.5484126825418614</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3107338230063263</v>
+        <v>0.2954817170182021</v>
       </c>
       <c r="J10" s="4">
-        <v>0.5268752735924671</v>
+        <v>0.5350111533968951</v>
       </c>
       <c r="K10" s="4">
         <v>70.00979026625485</v>
@@ -4310,13 +4310,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>61.72106824925816</v>
+        <v>61.12759643916914</v>
       </c>
       <c r="C11" s="3">
         <v>7.121661721068249</v>
       </c>
       <c r="D11" s="3">
-        <v>31.15727002967359</v>
+        <v>31.75074183976261</v>
       </c>
       <c r="E11" s="3">
         <v>10.08902077151335</v>
@@ -4325,16 +4325,16 @@
         <v>15.43026706231454</v>
       </c>
       <c r="G11" s="3">
-        <v>5.637982195845697</v>
+        <v>6.231454005934718</v>
       </c>
       <c r="H11" s="4">
-        <v>1.278325034879257</v>
+        <v>1.259358142955125</v>
       </c>
       <c r="I11" s="4">
-        <v>0.4812490740634772</v>
+        <v>0.2298429661804126</v>
       </c>
       <c r="J11" s="4">
-        <v>2.082717868382159</v>
+        <v>2.107613360052662</v>
       </c>
       <c r="K11" s="4">
         <v>70.53452835139981</v>
@@ -4360,13 +4360,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>67.35905044510386</v>
+        <v>66.17210682492582</v>
       </c>
       <c r="C12" s="3">
         <v>4.747774480712167</v>
       </c>
       <c r="D12" s="3">
-        <v>27.89317507418398</v>
+        <v>29.08011869436202</v>
       </c>
       <c r="E12" s="3">
         <v>5.934718100890208</v>
@@ -4375,16 +4375,16 @@
         <v>20.1780415430267</v>
       </c>
       <c r="G12" s="3">
-        <v>1.780415430267062</v>
+        <v>2.967359050445104</v>
       </c>
       <c r="H12" s="4">
-        <v>0.9149179545771449</v>
+        <v>0.9105843403221411</v>
       </c>
       <c r="I12" s="4">
-        <v>0.4324139218156585</v>
+        <v>0.2987514996515082</v>
       </c>
       <c r="J12" s="4">
-        <v>1.448848222206412</v>
+        <v>1.466804537994861</v>
       </c>
       <c r="K12" s="4">
         <v>70.60225277054452</v>
@@ -4428,13 +4428,13 @@
         <v>1.483679525222552</v>
       </c>
       <c r="H13" s="4">
-        <v>0.9049450706812165</v>
+        <v>0.9215972838210298</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2184266759559234</v>
+        <v>0.189996084755894</v>
       </c>
       <c r="J13" s="4">
-        <v>1.796860156854991</v>
+        <v>1.81481520170344</v>
       </c>
       <c r="K13" s="4">
         <v>70.69248470901719</v>
@@ -4478,13 +4478,13 @@
         <v>0.5934718100890208</v>
       </c>
       <c r="H14" s="4">
-        <v>0.6032807235318101</v>
+        <v>0.5733876881427031</v>
       </c>
       <c r="I14" s="4">
-        <v>0.2612449881314118</v>
+        <v>0.1967927914247659</v>
       </c>
       <c r="J14" s="4">
-        <v>0.4249694841102535</v>
+        <v>0.3795240559508867</v>
       </c>
       <c r="K14" s="4">
         <v>81.51204101818755</v>
@@ -4528,13 +4528,13 @@
         <v>0.2967359050445104</v>
       </c>
       <c r="H15" s="4">
-        <v>0.4948140653469624</v>
+        <v>0.4918973836485838</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1711234173189844</v>
+        <v>0.1587447925292578</v>
       </c>
       <c r="J15" s="4">
-        <v>0.3688215761392443</v>
+        <v>0.3568086052875247</v>
       </c>
       <c r="K15" s="4">
         <v>74.34960334282091</v>
@@ -4578,13 +4578,13 @@
         <v>0.5934718100890208</v>
       </c>
       <c r="H16" s="4">
-        <v>0.6204093008136342</v>
+        <v>0.5941000589445639</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2496808812400075</v>
+        <v>0.1980390082784663</v>
       </c>
       <c r="J16" s="4">
-        <v>0.4314788293075575</v>
+        <v>0.3932052970124577</v>
       </c>
       <c r="K16" s="4">
         <v>81.30351844001704</v>
@@ -4628,13 +4628,13 @@
         <v>0.2967359050445104</v>
       </c>
       <c r="H17" s="4">
-        <v>0.5489390719307577</v>
+        <v>0.5415653388532057</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2244290259866167</v>
+        <v>0.2112582775638863</v>
       </c>
       <c r="J17" s="4">
-        <v>0.4218910003828248</v>
+        <v>0.4142358196884543</v>
       </c>
       <c r="K17" s="4">
         <v>73.93841216011619</v>
@@ -5693,13 +5693,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C7" s="5">
         <v>2</v>
       </c>
       <c r="D7" s="5">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E7" s="5">
         <v>12</v>
@@ -5708,7 +5708,7 @@
         <v>60</v>
       </c>
       <c r="G7" s="5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H7" s="5">
         <v>12</v>
@@ -5737,13 +5737,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C8" s="5">
         <v>12</v>
       </c>
       <c r="D8" s="5">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E8" s="5">
         <v>0</v>
@@ -5752,7 +5752,7 @@
         <v>71</v>
       </c>
       <c r="G8" s="5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -5869,13 +5869,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C11" s="5">
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E11" s="5">
         <v>34</v>
@@ -5884,7 +5884,7 @@
         <v>52</v>
       </c>
       <c r="G11" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H11" s="5">
         <v>34</v>
@@ -5913,13 +5913,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C12" s="5">
         <v>16</v>
       </c>
       <c r="D12" s="5">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E12" s="5">
         <v>20</v>
@@ -5928,7 +5928,7 @@
         <v>68</v>
       </c>
       <c r="G12" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H12" s="5">
         <v>20</v>
@@ -6331,16 +6331,16 @@
         <v>8</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.567289293431915</v>
+        <v>-1.403364948779199</v>
       </c>
       <c r="O3" s="5">
         <v>124</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5781916307281724</v>
+        <v>0.5739785301456775</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2857647861783666</v>
+        <v>0.2566233434015818</v>
       </c>
       <c r="R3" s="5">
         <v>123</v>
@@ -6390,16 +6390,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5834387757914148</v>
+        <v>-0.7683739392432472</v>
       </c>
       <c r="O4" s="5">
         <v>77</v>
       </c>
       <c r="P4" s="4">
-        <v>1.159805043141614</v>
+        <v>1.185258339425241</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2285099447324392</v>
+        <v>0.1512033372120327</v>
       </c>
       <c r="R4" s="5">
         <v>74</v>
@@ -6572,16 +6572,16 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.326025901195134</v>
+        <v>-1.229078997250326</v>
       </c>
       <c r="O3" s="5">
         <v>118</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6562770057764341</v>
+        <v>0.6605872197692729</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3723823827864512</v>
+        <v>0.36148306913759</v>
       </c>
       <c r="R3" s="5">
         <v>117</v>
@@ -6631,16 +6631,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4113955749120533</v>
+        <v>-0.4290616934995342</v>
       </c>
       <c r="O4" s="5">
         <v>112</v>
       </c>
       <c r="P4" s="4">
-        <v>0.69490603704244</v>
+        <v>0.6918244166155277</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2206639628318489</v>
+        <v>0.2201425954350031</v>
       </c>
       <c r="R4" s="5">
         <v>112</v>
@@ -6813,16 +6813,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7081761642271932</v>
+        <v>-0.6346764260415512</v>
       </c>
       <c r="O3" s="5">
         <v>138</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4415189905141524</v>
+        <v>0.4408514817540535</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2530272284257897</v>
+        <v>0.2414739164245522</v>
       </c>
       <c r="R3" s="5">
         <v>137</v>
@@ -6872,16 +6872,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2242260190358011</v>
+        <v>-0.2947882508087787</v>
       </c>
       <c r="O4" s="5">
         <v>139</v>
       </c>
       <c r="P4" s="4">
-        <v>0.494067337432174</v>
+        <v>0.4825384504124256</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2159113377377592</v>
+        <v>0.2085764887717949</v>
       </c>
       <c r="R4" s="5">
         <v>139</v>
@@ -7054,16 +7054,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8477633907596893</v>
+        <v>-0.8405515673548507</v>
       </c>
       <c r="O3" s="5">
         <v>109</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7060100471931252</v>
+        <v>0.7070374872743591</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3275538397712039</v>
+        <v>0.3274876762537283</v>
       </c>
       <c r="R3" s="5">
         <v>109</v>
@@ -7113,16 +7113,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.05222000667834459</v>
+        <v>-0.1225031821668381</v>
       </c>
       <c r="O4" s="5">
         <v>119</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9862272514491282</v>
+        <v>0.9746672102371482</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3875847694527261</v>
+        <v>0.3810867438848282</v>
       </c>
       <c r="R4" s="5">
         <v>115</v>
@@ -7295,16 +7295,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7876173135995779</v>
+        <v>-0.6873365435421874</v>
       </c>
       <c r="O3" s="5">
         <v>140</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5030539161828125</v>
+        <v>0.4980399849397312</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2069919646433876</v>
+        <v>0.1851403361199818</v>
       </c>
       <c r="R3" s="5">
         <v>139</v>
@@ -7354,22 +7354,22 @@
         <v>12</v>
       </c>
       <c r="N4" s="4">
-        <v>0.5275223736994583</v>
+        <v>0.0142801564434194</v>
       </c>
       <c r="O4" s="5">
         <v>123</v>
       </c>
       <c r="P4" s="4">
-        <v>1.123765433036098</v>
+        <v>0.9850472111590678</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5704897792608232</v>
+        <v>0.2808458109353741</v>
       </c>
       <c r="R4" s="5">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="S4" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
